--- a/templates/polysani_homme_femme.xlsx
+++ b/templates/polysani_homme_femme.xlsx
@@ -1,29 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\modeles_reels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{655987DD-DF5B-47DD-A098-3AD0CB1909FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29733848-83A0-434B-8EF2-1ADA5118CD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" xr2:uid="{05BDB716-8B5C-4A0B-B991-B00EAA6E28D5}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" activeTab="2" xr2:uid="{05BDB716-8B5C-4A0B-B991-B00EAA6E28D5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Polysani Homme-Femme" sheetId="15" r:id="rId1"/>
+    <sheet name="Polysani Containex 5wc-3ur H-F" sheetId="10" r:id="rId1"/>
+    <sheet name="Polysani Homme-Femme" sheetId="15" r:id="rId2"/>
+    <sheet name="Polysani H-F avec urimat" sheetId="14" r:id="rId3"/>
+    <sheet name="Polysani H-F S03304 " sheetId="11" r:id="rId4"/>
+    <sheet name="Polysani H-F S10310" sheetId="12" r:id="rId5"/>
+    <sheet name="Polysani H-F S06309" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Polysani Homme-Femme'!$A$1:$F$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Polysani Containex 5wc-3ur H-F'!$A$1:$F$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Polysani H-F avec urimat'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Polysani H-F S03304 '!$A$1:$F$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Polysani H-F S06309'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Polysani H-F S10310'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Polysani Homme-Femme'!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="65">
   <si>
     <t>ETAT INTERIEUR</t>
   </si>
@@ -94,6 +115,9 @@
     <t>Interrupteur</t>
   </si>
   <si>
+    <t>Chauffe-eau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coffret électrique </t>
   </si>
   <si>
@@ -113,6 +137,9 @@
   </si>
   <si>
     <t>Lavabo + robinets</t>
+  </si>
+  <si>
+    <t>Groupe de sécurité</t>
   </si>
   <si>
     <t>Fenêtre</t>
@@ -160,17 +187,99 @@
     <t>Sanitaire : BLOC 6WC / 2UR / 2 LAVABOS (POLYSANI)</t>
   </si>
   <si>
+    <t xml:space="preserve">CLIENT : </t>
+  </si>
+  <si>
+    <t>S 03304</t>
+  </si>
+  <si>
+    <t>2 Urinoirs (sans eau)</t>
+  </si>
+  <si>
+    <t>Produit nettoyage pour urinoirs</t>
+  </si>
+  <si>
+    <t>Dévidoir papier
+Type Jumbo + Clé</t>
+  </si>
+  <si>
+    <t>CLEF CLOISONS INTERIEURES :  OUI     NON</t>
+  </si>
+  <si>
+    <t>CLEF BLOC SANI :  OUI        NON</t>
+  </si>
+  <si>
+    <t>S 10310</t>
+  </si>
+  <si>
+    <t>S 06309</t>
+  </si>
+  <si>
+    <t>S….................</t>
+  </si>
+  <si>
+    <t>Evacuation / Arrivée</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Visa contrôleur :                                        Date :</t>
+  </si>
+  <si>
+    <t>CLIENT : MAS SEEDS</t>
+  </si>
+  <si>
+    <t>CHANTIER : HAUT MAUCO</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLIENT :  </t>
   </si>
   <si>
     <t>S ….…………..…..</t>
+  </si>
+  <si>
+    <t>DIVERS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sanitaire : 
+BLOC 5WC / 3UR / 3 LAVABOS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(POLYSANI)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+S 22........................................
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Nom préparateur : …...................................</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -229,8 +338,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,12 +371,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -421,6 +553,21 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -483,217 +630,315 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,6 +958,718 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10241" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{679F82E1-F007-4ECF-7642-20FF53DFDF24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10242" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{608AD44A-1500-8A80-0DE0-4E0B1050E8A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4591050" y="0"/>
+          <a:ext cx="400050" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10244" name="Text Box 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A05AAD7-4C7B-4D03-BB29-F2130A8929C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6657975" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10523" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29E129C1-6CF4-5B3D-7969-FEEDF0BC37F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="2552700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10524" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE0EBD8-CDF3-9DC6-96E8-4BBDA1B0733C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3343275" y="4324350"/>
+          <a:ext cx="2276475" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10525" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{217202E5-2D61-A9A7-83B1-B517A41AF739}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4333875"/>
+          <a:ext cx="2400300" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD7CC70-924A-62E7-CC75-4FC4A6024144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3248025" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E05789-6CBA-B0A9-4DD1-358D0F372069}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>990600</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10528" name="Image 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D29E0EC7-3856-1BA5-BB6B-A75347CE309C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2466975" y="523875"/>
+          <a:ext cx="4229100" cy="2486025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10529" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1A60CB2-9FB9-DF32-7DBB-E7391FDBA331}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="38100" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1350,6 +2307,2558 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F2C6B9-BB9D-7ABC-04A1-D388AE8C1695}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4499E63F-97ED-3029-0776-C2E9C4BCC7E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4591050" y="0"/>
+          <a:ext cx="400050" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B0E6A7C-1BE9-380C-1267-C5B1BE1F207A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6657975" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14466" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1C25FD1-F46D-D0EE-4FEE-49371E139596}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="2552700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14467" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68513C28-5BA4-E807-A032-34A0F95BF4E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3343275" y="2543175"/>
+          <a:ext cx="2276475" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14468" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{452F7E7F-8BC0-9D56-D1E8-AD6C79BEA69D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2552700"/>
+          <a:ext cx="2400300" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79365A92-6109-397D-78A5-5B56503746E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FAAF125-8C5D-3FA1-AFC3-290832249B01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14471" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F012C1A8-DCD8-E62E-574E-C0184F52C7A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0251B4D8-510E-184D-CDFB-C737EF9F2647}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{251F87F2-A90D-FBA5-7688-196BA60A8DCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4591050" y="0"/>
+          <a:ext cx="400050" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36B85994-6FEB-17B8-E05D-9D70247C1469}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6657975" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11475" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E98A002-6C21-8AA2-BB3A-41B3A4009224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="2552700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11476" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AF521A8-3E4B-4F4B-6BA5-68990CFAD1C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3343275" y="2543175"/>
+          <a:ext cx="2276475" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11477" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DA09D3A-CCE2-CC05-CFB9-8BD1EF00DD92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2552700"/>
+          <a:ext cx="2400300" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8727034-4CED-0D40-8940-21F6C7874A43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD2731AA-2920-C6DB-178F-E12EC8B2B99C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11480" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F676C5B-891D-16D0-FA09-157CE0F4A106}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E794167-5DE1-E62A-E0E8-BB5122F20423}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{448F947F-EFD7-034E-6987-710CA5E289D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4591050" y="0"/>
+          <a:ext cx="400050" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34BC8455-FC7B-D208-0DBB-86F1B201FBDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6657975" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12472" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{714AA282-1495-4CDA-BB07-08812964F8BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="2552700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12473" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E630A6CA-40D4-21ED-890D-B0D0CE12301D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3343275" y="2543175"/>
+          <a:ext cx="2276475" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12474" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B294EDB8-8E17-DFDD-9A3D-95313317F7ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2552700"/>
+          <a:ext cx="2400300" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FA3747-BDB4-6F4F-89E1-0AFA9181684D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A643E11F-940F-FD0F-C575-E18C87F952A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12477" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B02F8D-72D4-F695-7CE9-EF5FD9E88CE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91B4DEB-3823-2456-F151-C3CA324465D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE36DA72-4C65-414E-2C4A-B7165F0C11AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4591050" y="0"/>
+          <a:ext cx="400050" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49ABF56B-D5EC-1B81-247A-D07506AF364C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6657975" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13460" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{370687C3-71F7-9DBD-6B96-EA0ADCB295BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="0"/>
+          <a:ext cx="2552700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13461" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22E486C5-A88E-F02E-91AE-2A9595B8F4B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3343275" y="2543175"/>
+          <a:ext cx="2276475" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13462" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA23B32C-D6E4-0909-4959-B3C8DC965B4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2552700"/>
+          <a:ext cx="2400300" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC670E9-B655-510B-2858-D8959A4C737C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41133D67-CBF8-5B3B-6439-5FAB01B82033}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13465" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6330B35-D5B1-80EA-C9D9-FE986A2587C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -1670,6 +5179,583 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C207120-8112-484B-9B89-80092112E71B}">
+  <sheetPr codeName="Feuil4">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D1" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" ht="183" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+    </row>
+    <row r="8" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="D8" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="65"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+    </row>
+    <row r="11" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="D17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="56"/>
+      <c r="E23" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="57"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="72"/>
+      <c r="C25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="73"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="61"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="80"/>
+      <c r="E29" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="81"/>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+    </row>
+    <row r="32" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="56"/>
+      <c r="E32" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="57"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="75"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+    </row>
+    <row r="35" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="76"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="83"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="82"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="82"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="82"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="82"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="82"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="47"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="82"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="82"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="82"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="50"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="23"/>
+    </row>
+    <row r="48" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="50"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="24"/>
+    </row>
+    <row r="49" spans="1:6" s="7" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="50"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="24"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="87"/>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="88"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="82"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="54"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="84"/>
+      <c r="C53" s="84"/>
+      <c r="D53" s="84"/>
+      <c r="E53" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="85"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="42">
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A27:B28"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5000EECF-4544-4614-98AB-6D24F12669E6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1677,548 +5763,570 @@
   <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
-    <col min="2" max="2" width="10.7109375" style="7" customWidth="1"/>
-    <col min="3" max="5" width="19.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D1" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="D1" s="89" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="D7" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="13"/>
-      <c r="D7" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="32"/>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-    </row>
-    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="64"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
     </row>
     <row r="12" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="D18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="66"/>
+      <c r="D18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="25" t="s">
+      <c r="D21" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>25</v>
+      <c r="F21" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="49" t="s">
+      <c r="B23" s="68"/>
+      <c r="C23" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="15" t="s">
+      <c r="D23" s="70"/>
+      <c r="E23" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43" t="s">
+      <c r="D24" s="56"/>
+      <c r="E24" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="44"/>
+      <c r="F24" s="56"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="5" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>26</v>
+      <c r="B26" s="72"/>
+      <c r="C26" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>26</v>
+      <c r="A27" s="73"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="55"/>
-      <c r="C28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>26</v>
+      <c r="B28" s="60"/>
+      <c r="C28" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>26</v>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="59"/>
-      <c r="C30" s="60" t="s">
+      <c r="A30" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="61"/>
-      <c r="E30" s="60" t="s">
+      <c r="D30" s="80"/>
+      <c r="E30" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="62"/>
+      <c r="F30" s="81"/>
     </row>
     <row r="31" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="23"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
     </row>
     <row r="33" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="43" t="s">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="43" t="s">
+      <c r="D33" s="56"/>
+      <c r="E33" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="44"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="11" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
+      <c r="A37" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="76"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="45" t="s">
+      <c r="A38" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="71"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="32"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="32"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
+      <c r="A41" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="71"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="32"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="A42" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="32"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="A43" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="71"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="A44" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="71"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="31"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="48"/>
     </row>
     <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="32"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B48" s="32"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="B48" s="71"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="32"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="20"/>
+      <c r="A50" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="50"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="23"/>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="21"/>
+      <c r="A51" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="50"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="71"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="22"/>
+    </row>
+    <row r="53" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="32"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="19"/>
-    </row>
-    <row r="53" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="40"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="87"/>
+      <c r="D53" s="87"/>
+      <c r="E53" s="87"/>
+      <c r="F53" s="88"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="33" t="s">
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="33"/>
+      <c r="F54" s="53"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+      <c r="A55" s="36"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="34" t="s">
+      <c r="A56" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="35" t="s">
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="35"/>
+      <c r="F56" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A26:B27"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A10:F10"/>
@@ -2228,17 +6336,2572 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094488" top="0.27559055118110237" bottom="0.11811023622047244" header="0.27559055118110237" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD168300-15F1-4CEC-AC7D-E1BE19D68B48}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D1" s="89" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="D7" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="100" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="100"/>
+      <c r="C8" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+    </row>
+    <row r="13" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="56"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="72"/>
+      <c r="C27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="73"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="81"/>
+    </row>
+    <row r="32" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+    </row>
+    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="75"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="71"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="71"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="71"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="71"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="71"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="71"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="103"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="71"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="71"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="71"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="71"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="71"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="71"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="50"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="23"/>
+    </row>
+    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="71"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="22"/>
+    </row>
+    <row r="57" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="88"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="53"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="36"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="99"/>
+    </row>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A26:B27"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="E8:F8"/>
+  </mergeCells>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094488" top="0.27559055118110237" bottom="0.11811023622047244" header="0.27559055118110237" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803ED28D-E7DC-4314-B958-459A4E1A1C3E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D1" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="D7" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="65"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="56"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="72"/>
+      <c r="C27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="73"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="81"/>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+    </row>
+    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="75"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="82"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="82"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="82"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="82"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="82"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="104"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="82"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="82"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="82"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="82"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="82"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="82"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="50"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="23"/>
+    </row>
+    <row r="55" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="82"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="22"/>
+    </row>
+    <row r="57" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="88"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="54"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="85"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A36:B37"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:F58"/>
+  </mergeCells>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094488" top="0.27559055118110237" bottom="0.11811023622047244" header="0.27559055118110237" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F14E256-557A-4518-9C15-371F37F215B9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D1" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="D7" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="65"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="56"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="72"/>
+      <c r="C27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="73"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="81"/>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+    </row>
+    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="75"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="82"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="82"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="82"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="82"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="82"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="104"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="82"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="82"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="82"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="82"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="82"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="82"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="50"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="23"/>
+    </row>
+    <row r="55" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="82"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="22"/>
+    </row>
+    <row r="57" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="88"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="54"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="85"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D9:F9"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0.27559055118110237" bottom="0.11811023622047245" header="0.27559055118110237" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5319D391-4BD0-4EB0-AD41-376FD29BD5AA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="10.7109375" style="9" customWidth="1"/>
+    <col min="3" max="5" width="19.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D1" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="D7" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="65"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="D19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="56"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="72"/>
+      <c r="C27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="73"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="81"/>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+    </row>
+    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="75"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="82"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="82"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="82"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="82"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="82"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="104"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="82"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="82"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="82"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="82"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="82"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="82"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="50"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="23"/>
+    </row>
+    <row r="55" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" s="7" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="82"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="22"/>
+    </row>
+    <row r="57" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="88"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="54"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="85"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
@@ -2250,15 +8913,20 @@
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:F60"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.23622047244094488" top="0.27559055118110237" bottom="0.11811023622047244" header="0.27559055118110237" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
